--- a/rabbit-web-app/public/records/truck_multi_services_bulk_sample.xlsx
+++ b/rabbit-web-app/public/records/truck_multi_services_bulk_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Bulk Multi-Services Trucks" sheetId="1" r:id="rId1"/>
+    <sheet name="Truck Services" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,19 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="50.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,10 +445,10 @@
         <v>152000</v>
       </c>
       <c r="E2" t="str">
-        <v>90 Days Inspection, AC Compressor, AC Drier, Air Dryer Filter, Air Filter, Alternator, Battery Change, Brake Drive, Grease Truck &amp; King Pins, Oil Change / Service</v>
+        <v>90 Days Inspection</v>
       </c>
       <c r="F2" t="str">
-        <v>2nd Axle (D/S), 3rd Axle (P/S)</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v>Volvo Fleet Center</v>
@@ -468,176 +456,336 @@
       <c r="H2" t="str">
         <v>INV-TK-1001</v>
       </c>
-      <c r="I2" t="str">
-        <v>2450.00</v>
+      <c r="I2">
+        <v>2450</v>
       </c>
       <c r="J2" t="str">
-        <v>Comprehensive 10-point service including drive brakes and oil service</v>
+        <v>Comprehensive service including drive brakes and AC inspection</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>CH001</v>
+        <v>ACHA9999</v>
       </c>
       <c r="B3" t="str">
-        <v>FREIGHTLINER</v>
+        <v>VOLVO</v>
       </c>
       <c r="C3" t="str">
         <v>2026-08-19</v>
       </c>
       <c r="D3">
-        <v>128500</v>
+        <v>152000</v>
       </c>
       <c r="E3" t="str">
-        <v>90 Days Inspection, AC Compressor, AC Drier, AC Filter (Outside), AC Filter Bunk (early if have pets), Air Compressor, Air Dryer Assembly, Air Dryer Filter, Air Filter, Alignment, Alternator, Annual Inspection, Battery Change, Brake Steer, Bushing Steer, DEF Filter (Small one), Grease Truck &amp; King Pins, Nox Sensor Inlet, Oil Change / Service, Shock</v>
+        <v>AC Compressor</v>
       </c>
       <c r="F3" t="str">
-        <v>Steer Axle (D/S), Steer Axle (P/S), 2nd Axle (D/S)</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Freightliner Express</v>
+        <v>Volvo Fleet Center</v>
       </c>
       <c r="H3" t="str">
-        <v>INV-TK-1002</v>
-      </c>
-      <c r="I3" t="str">
-        <v>4850.00</v>
+        <v>INV-TK-1001</v>
+      </c>
+      <c r="I3">
+        <v>2450</v>
       </c>
       <c r="J3" t="str">
-        <v>20-service major overhaul including steer brakes, shocks, and filters</v>
+        <v>Comprehensive service including drive brakes and AC inspection</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CH002</v>
+        <v>ACHA9999</v>
       </c>
       <c r="B4" t="str">
-        <v>INTERNATIONAL</v>
+        <v>VOLVO</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-19</v>
       </c>
       <c r="D4">
-        <v>185000</v>
+        <v>152000</v>
       </c>
       <c r="E4" t="str">
-        <v>90 Days Inspection, AC Compressor, AC Drier, AC Filter (Outside), AC Filter Cabin (early if have pets), AHI Clean/Replace (7th Injector), Air Compressor, Air Dryer Assembly, Air Dryer Filter, Air Filter, Alignment, Alternator, Annual Inspection, Battery Change, Brake Drive, Brake Steer, Bushing Drive, Bushing Steer, Crankcase Breather, DEF Filter (Small one), DEF Pump, Differential /Axle Gasket, Differential /Axle Oil, DPF Clean (~85), Fuel Pump, Grease Truck &amp; King Pins, Hub Seal, King Pins, Nox Sensor Inlet, Oil Change / Service</v>
+        <v>Brake Drive</v>
       </c>
       <c r="F4" t="str">
-        <v>2nd Axle (D/S), 3rd Axle (P/S), Steer Axle (D/S), 2nd Axle</v>
+        <v>2nd Axle (D/S), 2nd Axle (P/S)</v>
       </c>
       <c r="G4" t="str">
-        <v>International Service Hub</v>
+        <v>Volvo Fleet Center</v>
       </c>
       <c r="H4" t="str">
-        <v>INV-TK-1003</v>
-      </c>
-      <c r="I4" t="str">
-        <v>7950.00</v>
+        <v>INV-TK-1001</v>
+      </c>
+      <c r="I4">
+        <v>2450</v>
       </c>
       <c r="J4" t="str">
-        <v>Complete 30-service preventive maintenance and axle inspection</v>
+        <v>Comprehensive service including drive brakes and AC inspection</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CH003</v>
+        <v>CH001</v>
       </c>
       <c r="B5" t="str">
         <v>FREIGHTLINER</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-08-18</v>
+        <v>2026-08-19</v>
       </c>
       <c r="D5">
-        <v>143200</v>
+        <v>128500</v>
       </c>
       <c r="E5" t="str">
-        <v>Air Filter, Alignment, Battery Change, DEF Filter (Small one), Grease Truck &amp; King Pins, Nox Sensor Outlet, Oil Change / Service, Radiator, Steer Tires, Water / Fuel Separator</v>
+        <v>Oil Change / Service</v>
       </c>
       <c r="F5" t="str">
-        <v>Michelin, Bridgestone</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v>Freightliner Express</v>
       </c>
       <c r="H5" t="str">
-        <v>INV-TK-1004</v>
-      </c>
-      <c r="I5" t="str">
-        <v>3120.00</v>
+        <v>INV-TK-1002</v>
+      </c>
+      <c r="I5">
+        <v>1850</v>
       </c>
       <c r="J5" t="str">
-        <v>10-service package with Michelin steer tires and cooling service</v>
+        <v>Full synthetic oil change and steer axle brake rebuild</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>DRY098JJHH</v>
+        <v>CH001</v>
       </c>
       <c r="B6" t="str">
-        <v>MACK</v>
+        <v>FREIGHTLINER</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-08-17</v>
+        <v>2026-08-19</v>
       </c>
       <c r="D6">
-        <v>168000</v>
+        <v>128500</v>
       </c>
       <c r="E6" t="str">
-        <v>90 Days Inspection, AC Compressor, AC Filter (Outside), Air Dryer Filter, Air Filter, Alignment, Alternator, Battery Change, Brake Drive, Bushing Drive, Crankcase Breather, DEF Filter (Small one), Grease Truck &amp; King Pins, Hub Seal, Oil Change / Service, Power Steering OIL &amp; filter, Radiator, Rotor, S-Cam, Slack Adjuster</v>
+        <v>Brake Steer</v>
       </c>
       <c r="F6" t="str">
-        <v>2nd Axle (D/S), 3rd Axle (D/S), Steer Axle (P/S), 2nd Axle (P/S)</v>
+        <v>Steer Axle (D/S), Steer Axle (P/S)</v>
       </c>
       <c r="G6" t="str">
-        <v>Mack Truck Care</v>
+        <v>Freightliner Express</v>
       </c>
       <c r="H6" t="str">
-        <v>INV-TK-1005</v>
-      </c>
-      <c r="I6" t="str">
-        <v>5420.00</v>
+        <v>INV-TK-1002</v>
+      </c>
+      <c r="I6">
+        <v>1850</v>
       </c>
       <c r="J6" t="str">
-        <v>20-service brake and suspension rebuild with S-Cam and slack adjusters</v>
+        <v>Full synthetic oil change and steer axle brake rebuild</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>RMSS123</v>
+        <v>CH001</v>
       </c>
       <c r="B7" t="str">
         <v>FREIGHTLINER</v>
       </c>
       <c r="C7" t="str">
+        <v>2026-08-19</v>
+      </c>
+      <c r="D7">
+        <v>128500</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Air Filter</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>Freightliner Express</v>
+      </c>
+      <c r="H7" t="str">
+        <v>INV-TK-1002</v>
+      </c>
+      <c r="I7">
+        <v>1850</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Full synthetic oil change and steer axle brake rebuild</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CH003</v>
+      </c>
+      <c r="B8" t="str">
+        <v>FREIGHTLINER</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-08-18</v>
+      </c>
+      <c r="D8">
+        <v>143200</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Steer Tires</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Michelin, Bridgestone</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Freightliner Express</v>
+      </c>
+      <c r="H8" t="str">
+        <v>INV-TK-1003</v>
+      </c>
+      <c r="I8">
+        <v>3120</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Front steer tires replacement and 3-axle laser alignment</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CH003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>FREIGHTLINER</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-08-18</v>
+      </c>
+      <c r="D9">
+        <v>143200</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Alignment</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>Freightliner Express</v>
+      </c>
+      <c r="H9" t="str">
+        <v>INV-TK-1003</v>
+      </c>
+      <c r="I9">
+        <v>3120</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Front steer tires replacement and 3-axle laser alignment</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>DRY098JJHH</v>
+      </c>
+      <c r="B10" t="str">
+        <v>MACK</v>
+      </c>
+      <c r="C10" t="str">
         <v>2026-08-17</v>
       </c>
-      <c r="D7">
-        <v>135400</v>
-      </c>
-      <c r="E7" t="str">
-        <v>90 Days Inspection, AC Compressor, AC Drier, AC Filter (Outside), AC Filter Bunk (early if have pets), AC Filter Cabin (early if have pets), Air Compressor, Air Dryer Assembly, Air Dryer Filter, Air Filter, Alignment, Alternator, Annual Inspection, Battery Change, Brake Steer, Bushing Steer, DEF Filter (Small one), DEF Pump, Differential /Axle Oil, Differential /Axle Seal, Fuel Pump, Grease Truck &amp; King Pins, Hub Seal, Nox Sensor Inlet, Nox Sensor Outlet, Oil Change / Service, Power Steering OIL &amp; filter, Rotor, Shock, Slack Adjuster</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Steer Axle (D/S), 2nd Axle Input, 3rd Axle input, 2nd Axle (P/S)</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Speedy Fleet Service</v>
-      </c>
-      <c r="H7" t="str">
-        <v>INV-TK-1006</v>
-      </c>
-      <c r="I7" t="str">
-        <v>8200.00</v>
-      </c>
-      <c r="J7" t="str">
-        <v>30-service comprehensive fleet maintenance with differential seals and rotors</v>
+      <c r="D10">
+        <v>168000</v>
+      </c>
+      <c r="E10" t="str">
+        <v>90 Days Inspection</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>Mack Truck Care</v>
+      </c>
+      <c r="H10" t="str">
+        <v>INV-TK-1004</v>
+      </c>
+      <c r="I10">
+        <v>4200</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Mack preventive maintenance with drive axle hub seals</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>DRY098JJHH</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MACK</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="D11">
+        <v>168000</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Hub Seal</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2nd Axle (D/S), 3rd Axle (D/S)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Mack Truck Care</v>
+      </c>
+      <c r="H11" t="str">
+        <v>INV-TK-1004</v>
+      </c>
+      <c r="I11">
+        <v>4200</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Mack preventive maintenance with drive axle hub seals</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>DRY098JJHH</v>
+      </c>
+      <c r="B12" t="str">
+        <v>MACK</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="D12">
+        <v>168000</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Oil Change / Service</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>Mack Truck Care</v>
+      </c>
+      <c r="H12" t="str">
+        <v>INV-TK-1004</v>
+      </c>
+      <c r="I12">
+        <v>4200</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Mack preventive maintenance with drive axle hub seals</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
   </ignoredErrors>
 </worksheet>
 </file>